--- a/PREGAME/1. ELICITACION/1.3 Historias de Usuario/MTZHU_G1_V8.0.xlsx
+++ b/PREGAME/1. ELICITACION/1.3 Historias de Usuario/MTZHU_G1_V8.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Esteban\Documents\Documentos\PREGRADO SI-ABR26-AGO26\MDSW\30693_MDS_G1\PREGAME\1. ELICITACION\1.3 Historias de Usuario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC2B840B-8868-4276-AC8B-1BED1BA3DF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E6C3EE0-FBD4-4C0C-B050-A68584ABB8A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1973,7 +1973,7 @@
         <v>91</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I15" s="38">
         <v>5</v>
